--- a/www/data-entry-template/GLATAR_data_entry_template_v17_long.xlsx
+++ b/www/data-entry-template/GLATAR_data_entry_template_v17_long.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benhlina/Library/CloudStorage/Dropbox/GitHub/GLATAR-App/www/data-entry-template/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{499185CE-00B5-1B42-84BE-CC7F8952EE4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04AB0F68-1943-7547-9CE0-DB5C1CF86938}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="640" windowWidth="34560" windowHeight="19460" xr2:uid="{DE6F8925-643B-304C-8933-23D4A9123DA3}"/>
+    <workbookView xWindow="-25580" yWindow="1720" windowWidth="25600" windowHeight="19460" xr2:uid="{DE6F8925-643B-304C-8933-23D4A9123DA3}"/>
   </bookViews>
   <sheets>
     <sheet name="data_dictionary" sheetId="1" r:id="rId1"/>
@@ -1087,9 +1087,6 @@
     <t>amino_acid_measurement</t>
   </si>
   <si>
-    <t>as in: 2.4 ‰; format; integer</t>
-  </si>
-  <si>
     <t>Percent amino acid of a sample</t>
   </si>
   <si>
@@ -1100,9 +1097,6 @@
   </si>
   <si>
     <t>amino_acid_type</t>
-  </si>
-  <si>
-    <t>as in: Alanine: format; character</t>
   </si>
   <si>
     <t>Type of amino acid</t>
@@ -1117,16 +1111,10 @@
     <t>mercury_ppm</t>
   </si>
   <si>
-    <t>as in: 0.14; format: integer</t>
-  </si>
-  <si>
     <t>Mercury measurement</t>
   </si>
   <si>
     <t>mercury_type</t>
-  </si>
-  <si>
-    <t>as in: methylmercury: format; character</t>
   </si>
   <si>
     <t xml:space="preserve">Type of mercury </t>
@@ -1139,9 +1127,6 @@
   </si>
   <si>
     <t>pcb_congener_ng_g</t>
-  </si>
-  <si>
-    <t>as in: 0.20; format: integer</t>
   </si>
   <si>
     <t>Polychlorimated biphenols (PCB) congener measurement</t>
@@ -1216,9 +1201,6 @@
     <t>as in: Th (free thiamine); format: character</t>
   </si>
   <si>
-    <t>as in: 0.12; fromat: numeric</t>
-  </si>
-  <si>
     <t>as in: 0.6; format: numeric</t>
   </si>
   <si>
@@ -1229,6 +1211,24 @@
   </si>
   <si>
     <t>Standard deviation of Thiaminase activity if reported as mean</t>
+  </si>
+  <si>
+    <t>as in: Alanine; format: character</t>
+  </si>
+  <si>
+    <t>as in: methylmercury; format: character</t>
+  </si>
+  <si>
+    <t>as in: 0.14; format: numeric</t>
+  </si>
+  <si>
+    <t>as in: 0.20; format: numeric</t>
+  </si>
+  <si>
+    <t>as in: 2.4 ‰; format: numeric</t>
+  </si>
+  <si>
+    <t>as in: 0.12; format: numeric</t>
   </si>
 </sst>
 </file>
@@ -1456,7 +1456,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1549,18 +1549,10 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1583,6 +1575,13 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1935,20 +1934,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="48" t="s">
         <v>211</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
     </row>
     <row r="2" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="48" t="s">
         <v>192</v>
       </c>
-      <c r="B2" s="40"/>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
+      <c r="B2" s="48"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="21" t="s">
@@ -2003,7 +2002,7 @@
         <v>171</v>
       </c>
       <c r="D7" s="24" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
@@ -2017,7 +2016,7 @@
         <v>66</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="28" x14ac:dyDescent="0.2">
@@ -2059,7 +2058,7 @@
         <v>171</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
@@ -2325,7 +2324,7 @@
         <v>160</v>
       </c>
       <c r="D30" s="30" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
@@ -2406,7 +2405,7 @@
         <v>186</v>
       </c>
       <c r="C36" s="30" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="D36" s="33" t="s">
         <v>214</v>
@@ -2521,7 +2520,7 @@
         <v>79</v>
       </c>
       <c r="D44" s="30" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
@@ -2644,10 +2643,10 @@
         <v>109</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
@@ -2731,7 +2730,7 @@
         <v>180</v>
       </c>
       <c r="D59" s="30" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
@@ -3022,10 +3021,10 @@
         <v>249</v>
       </c>
       <c r="C80" s="30" t="s">
+        <v>296</v>
+      </c>
+      <c r="D80" s="33" t="s">
         <v>250</v>
-      </c>
-      <c r="D80" s="33" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="81" spans="1:4" ht="42" x14ac:dyDescent="0.2">
@@ -3033,13 +3032,13 @@
         <v>248</v>
       </c>
       <c r="B81" s="30" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C81" s="30" t="s">
         <v>243</v>
       </c>
       <c r="D81" s="33" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.2">
@@ -3047,153 +3046,153 @@
         <v>248</v>
       </c>
       <c r="B82" s="30" t="s">
+        <v>253</v>
+      </c>
+      <c r="C82" s="30" t="s">
+        <v>292</v>
+      </c>
+      <c r="D82" s="33" t="s">
         <v>254</v>
-      </c>
-      <c r="C82" s="30" t="s">
-        <v>255</v>
-      </c>
-      <c r="D82" s="33" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A83" s="30" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="B83" s="30" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C83" s="30" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="D83" s="30" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="84" spans="1:4" ht="28" x14ac:dyDescent="0.2">
       <c r="A84" s="30" t="s">
-        <v>275</v>
-      </c>
-      <c r="B84" s="43" t="s">
-        <v>286</v>
+        <v>270</v>
+      </c>
+      <c r="B84" s="40" t="s">
+        <v>281</v>
       </c>
       <c r="C84" s="30" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="D84" s="33" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
     </row>
     <row r="85" spans="1:4" ht="42" x14ac:dyDescent="0.2">
       <c r="A85" s="30" t="s">
-        <v>275</v>
-      </c>
-      <c r="B85" s="43" t="s">
+        <v>270</v>
+      </c>
+      <c r="B85" s="40" t="s">
+        <v>280</v>
+      </c>
+      <c r="C85" s="30" t="s">
+        <v>287</v>
+      </c>
+      <c r="D85" s="33" t="s">
         <v>285</v>
-      </c>
-      <c r="C85" s="30" t="s">
-        <v>292</v>
-      </c>
-      <c r="D85" s="33" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A86" s="30" t="s">
-        <v>275</v>
-      </c>
-      <c r="B86" s="43" t="s">
-        <v>287</v>
+        <v>270</v>
+      </c>
+      <c r="B86" s="40" t="s">
+        <v>282</v>
       </c>
       <c r="C86" s="30" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="D86" s="30" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A87" s="30" t="s">
-        <v>275</v>
-      </c>
-      <c r="B87" s="43" t="s">
-        <v>288</v>
+        <v>270</v>
+      </c>
+      <c r="B87" s="40" t="s">
+        <v>283</v>
       </c>
       <c r="C87" s="30" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="D87" s="30" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A88" s="30" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="B88" s="30" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C88" s="30" t="s">
-        <v>260</v>
+        <v>294</v>
       </c>
       <c r="D88" s="30" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A89" s="30" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="B89" s="30" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C89" s="30" t="s">
-        <v>263</v>
+        <v>293</v>
       </c>
       <c r="D89" s="30" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A90" s="30" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="B90" s="30" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="C90" s="30" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="D90" s="30" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A91" s="30" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="B91" s="30" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="C91" s="30" t="s">
-        <v>268</v>
+        <v>295</v>
       </c>
       <c r="D91" s="30" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A92" s="30" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="B92" s="30" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="C92" s="30" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="D92" s="30" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
     </row>
   </sheetData>
@@ -3217,27 +3216,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="19" x14ac:dyDescent="0.25">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="49" t="s">
         <v>202</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
       <c r="D1" s="10" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="49" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
       <c r="D2" s="11"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="41"/>
-      <c r="B3" s="41"/>
-      <c r="C3" s="41"/>
+      <c r="A3" s="49"/>
+      <c r="B3" s="49"/>
+      <c r="C3" s="49"/>
       <c r="D3" s="11" t="s">
         <v>206</v>
       </c>
@@ -3283,27 +3282,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="19" x14ac:dyDescent="0.25">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="49" t="s">
         <v>190</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
       <c r="D1" s="10" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="49" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
       <c r="D2" s="11"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A3" s="41"/>
-      <c r="B3" s="42"/>
-      <c r="C3" s="42"/>
+      <c r="A3" s="49"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="50"/>
       <c r="D3" s="11" t="s">
         <v>25</v>
       </c>
@@ -44261,7 +44260,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED99CF4A-5D49-794D-A1CB-3B08F37AF445}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:BT29"/>
+  <dimension ref="A1:BT22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20.5" customWidth="1"/>
@@ -44313,27 +44312,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:72" ht="19" x14ac:dyDescent="0.25">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="49" t="s">
         <v>189</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
       <c r="D1" s="5" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="2" spans="1:72" x14ac:dyDescent="0.2">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="49" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
       <c r="D2" s="6"/>
     </row>
     <row r="3" spans="1:72" x14ac:dyDescent="0.2">
-      <c r="A3" s="41"/>
-      <c r="B3" s="42"/>
-      <c r="C3" s="42"/>
+      <c r="A3" s="49"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="50"/>
       <c r="D3" s="6" t="s">
         <v>25</v>
       </c>
@@ -44370,14 +44369,14 @@
       <c r="BI4" s="38"/>
       <c r="BJ4" s="38"/>
       <c r="BK4" s="38" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="BL4" s="38"/>
       <c r="BM4" s="38"/>
       <c r="BN4" s="38"/>
       <c r="BO4" s="38"/>
       <c r="BP4" s="38" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="BQ4" s="38"/>
       <c r="BR4" s="38"/>
@@ -44385,16 +44384,16 @@
       <c r="BT4" s="38"/>
     </row>
     <row r="5" spans="1:72" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="46" t="s">
+      <c r="A5" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="46" t="s">
+      <c r="B5" s="42" t="s">
         <v>80</v>
       </c>
       <c r="C5" s="36" t="s">
         <v>194</v>
       </c>
-      <c r="D5" s="47" t="s">
+      <c r="D5" s="43" t="s">
         <v>199</v>
       </c>
       <c r="E5" s="36" t="s">
@@ -44406,10 +44405,10 @@
       <c r="G5" s="36" t="s">
         <v>135</v>
       </c>
-      <c r="H5" s="48" t="s">
+      <c r="H5" s="44" t="s">
         <v>195</v>
       </c>
-      <c r="I5" s="48" t="s">
+      <c r="I5" s="44" t="s">
         <v>193</v>
       </c>
       <c r="J5" s="36" t="s">
@@ -44424,7 +44423,7 @@
       <c r="M5" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="N5" s="48" t="s">
+      <c r="N5" s="44" t="s">
         <v>13</v>
       </c>
       <c r="O5" s="36" t="s">
@@ -44442,22 +44441,22 @@
       <c r="S5" s="36" t="s">
         <v>201</v>
       </c>
-      <c r="T5" s="49" t="s">
+      <c r="T5" s="45" t="s">
         <v>72</v>
       </c>
-      <c r="U5" s="49" t="s">
+      <c r="U5" s="45" t="s">
         <v>73</v>
       </c>
-      <c r="V5" s="48" t="s">
+      <c r="V5" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="W5" s="50" t="s">
+      <c r="W5" s="46" t="s">
         <v>71</v>
       </c>
-      <c r="X5" s="49" t="s">
+      <c r="X5" s="45" t="s">
         <v>122</v>
       </c>
-      <c r="Y5" s="48" t="s">
+      <c r="Y5" s="44" t="s">
         <v>17</v>
       </c>
       <c r="Z5" s="36" t="s">
@@ -44469,16 +44468,16 @@
       <c r="AB5" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="AC5" s="51" t="s">
+      <c r="AC5" s="47" t="s">
         <v>197</v>
       </c>
-      <c r="AD5" s="51" t="s">
+      <c r="AD5" s="47" t="s">
         <v>198</v>
       </c>
-      <c r="AE5" s="51" t="s">
+      <c r="AE5" s="47" t="s">
         <v>67</v>
       </c>
-      <c r="AF5" s="51" t="s">
+      <c r="AF5" s="47" t="s">
         <v>109</v>
       </c>
       <c r="AG5" s="36" t="s">
@@ -44493,16 +44492,16 @@
       <c r="AJ5" s="36" t="s">
         <v>116</v>
       </c>
-      <c r="AK5" s="49" t="s">
+      <c r="AK5" s="45" t="s">
         <v>139</v>
       </c>
-      <c r="AL5" s="49" t="s">
+      <c r="AL5" s="45" t="s">
         <v>140</v>
       </c>
-      <c r="AM5" s="49" t="s">
+      <c r="AM5" s="45" t="s">
         <v>143</v>
       </c>
-      <c r="AN5" s="49" t="s">
+      <c r="AN5" s="45" t="s">
         <v>144</v>
       </c>
       <c r="AO5" s="36" t="s">
@@ -44566,92 +44565,53 @@
         <v>249</v>
       </c>
       <c r="BI5" s="39" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="BJ5" s="39" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="BK5" s="39" t="s">
+        <v>255</v>
+      </c>
+      <c r="BL5" s="39" t="s">
+        <v>281</v>
+      </c>
+      <c r="BM5" s="39" t="s">
+        <v>280</v>
+      </c>
+      <c r="BN5" s="39" t="s">
+        <v>282</v>
+      </c>
+      <c r="BO5" s="39" t="s">
+        <v>283</v>
+      </c>
+      <c r="BP5" s="39" t="s">
         <v>257</v>
       </c>
-      <c r="BL5" s="39" t="s">
-        <v>286</v>
-      </c>
-      <c r="BM5" s="39" t="s">
-        <v>285</v>
-      </c>
-      <c r="BN5" s="39" t="s">
-        <v>287</v>
-      </c>
-      <c r="BO5" s="39" t="s">
-        <v>288</v>
-      </c>
-      <c r="BP5" s="39" t="s">
+      <c r="BQ5" s="39" t="s">
         <v>259</v>
       </c>
-      <c r="BQ5" s="39" t="s">
-        <v>262</v>
-      </c>
       <c r="BR5" s="39" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="BS5" s="39" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="BT5" s="39" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="13" spans="1:72" x14ac:dyDescent="0.2">
-      <c r="BK13" s="44"/>
-    </row>
-    <row r="14" spans="1:72" x14ac:dyDescent="0.2">
-      <c r="BK14" s="44"/>
-    </row>
-    <row r="15" spans="1:72" x14ac:dyDescent="0.2">
-      <c r="BK15" s="44"/>
-    </row>
-    <row r="16" spans="1:72" x14ac:dyDescent="0.2">
-      <c r="BK16" s="44"/>
-    </row>
-    <row r="17" spans="63:63" x14ac:dyDescent="0.2">
-      <c r="BK17" s="44"/>
-    </row>
-    <row r="18" spans="63:63" x14ac:dyDescent="0.2">
-      <c r="BK18" s="44"/>
+        <v>265</v>
+      </c>
     </row>
     <row r="19" spans="63:63" x14ac:dyDescent="0.2">
-      <c r="BK19" s="45"/>
+      <c r="BK19" s="41"/>
     </row>
     <row r="20" spans="63:63" x14ac:dyDescent="0.2">
-      <c r="BK20" s="45"/>
+      <c r="BK20" s="41"/>
     </row>
     <row r="21" spans="63:63" x14ac:dyDescent="0.2">
-      <c r="BK21" s="45"/>
+      <c r="BK21" s="41"/>
     </row>
     <row r="22" spans="63:63" x14ac:dyDescent="0.2">
-      <c r="BK22" s="45"/>
-    </row>
-    <row r="23" spans="63:63" x14ac:dyDescent="0.2">
-      <c r="BK23" s="44"/>
-    </row>
-    <row r="24" spans="63:63" x14ac:dyDescent="0.2">
-      <c r="BK24" s="44"/>
-    </row>
-    <row r="25" spans="63:63" x14ac:dyDescent="0.2">
-      <c r="BK25" s="44"/>
-    </row>
-    <row r="26" spans="63:63" x14ac:dyDescent="0.2">
-      <c r="BK26" s="44"/>
-    </row>
-    <row r="27" spans="63:63" x14ac:dyDescent="0.2">
-      <c r="BK27" s="44"/>
-    </row>
-    <row r="28" spans="63:63" x14ac:dyDescent="0.2">
-      <c r="BK28" s="44"/>
-    </row>
-    <row r="29" spans="63:63" x14ac:dyDescent="0.2">
-      <c r="BK29" s="44"/>
+      <c r="BK22" s="41"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1"/>

--- a/www/data-entry-template/GLATAR_data_entry_template_v17_long.xlsx
+++ b/www/data-entry-template/GLATAR_data_entry_template_v17_long.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benhlina/Library/CloudStorage/Dropbox/GitHub/GLATAR-App/www/data-entry-template/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04AB0F68-1943-7547-9CE0-DB5C1CF86938}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96CFF9D4-7418-D740-BFA2-EC78283C658F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25580" yWindow="1720" windowWidth="25600" windowHeight="19460" xr2:uid="{DE6F8925-643B-304C-8933-23D4A9123DA3}"/>
+    <workbookView xWindow="3040" yWindow="600" windowWidth="35040" windowHeight="16300" xr2:uid="{DE6F8925-643B-304C-8933-23D4A9123DA3}"/>
   </bookViews>
   <sheets>
     <sheet name="data_dictionary" sheetId="1" r:id="rId1"/>
@@ -44621,7 +44621,7 @@
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A3:C3"/>
   </mergeCells>
-  <dataValidations count="19">
+  <dataValidations count="20">
     <dataValidation showInputMessage="1" showErrorMessage="1" errorTitle="Unknown sex " error="You have entered an unknown value for sex " promptTitle="Sex" sqref="L5" xr:uid="{61B800F7-85EA-B74C-8D79-217EB2BB8728}"/>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R6:R999" xr:uid="{C1262AB6-4400-D04A-976B-8F918C2989AD}">
       <formula1>"Total, Fork, Standard, Carapace"</formula1>
@@ -44653,7 +44653,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M6:M1000" xr:uid="{15E17D1F-987D-C745-9314-52B2C8C66A40}">
       <formula1>"fry, larva, juvenile, adult "</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V6:V10000" xr:uid="{E2A68CBD-EDB8-0D48-9B6E-B29E20DC1B19}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V1001:V10000" xr:uid="{E2A68CBD-EDB8-0D48-9B6E-B29E20DC1B19}">
       <formula1>"belly flap, blood, carcass, cleithra, eye lens, fin, gonad, liver, muscle, otolith, scale, spine, stomach, viscera, whole body, whole body (gonads removed), whole body (stomach removed)"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BC6:BC10000" xr:uid="{6BCDA29E-00AD-DC44-9456-909A8798CD81}">
@@ -44677,6 +44677,9 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BM6:BM10000" xr:uid="{73E98200-DF79-B04A-8673-08ACB9A22C3B}">
       <formula1>"Th (free thiamine), TMP (thiamine monophosphate), TPP (thiamine pyrophosphate), TTh (total thiamine)"</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V6:V1000" xr:uid="{46AB659B-2A50-3441-8038-5315F30CB679}">
+      <formula1>"belly flap, blood, carcass, cleithra, egg, eye lens, fin, gonad, heart, liver, muscle, otolith, scale, spine, stomach, viscera, whole body, whole body (gonads removed), whole body (stomach removed)"</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>

--- a/www/data-entry-template/GLATAR_data_entry_template_v17_long.xlsx
+++ b/www/data-entry-template/GLATAR_data_entry_template_v17_long.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benhlina/Library/CloudStorage/Dropbox/GitHub/GLATAR-App/www/data-entry-template/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96CFF9D4-7418-D740-BFA2-EC78283C658F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6106D211-E847-7B4B-A568-5680A3C3D270}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3040" yWindow="600" windowWidth="35040" windowHeight="16300" xr2:uid="{DE6F8925-643B-304C-8933-23D4A9123DA3}"/>
   </bookViews>

--- a/www/data-entry-template/GLATAR_data_entry_template_v17_long.xlsx
+++ b/www/data-entry-template/GLATAR_data_entry_template_v17_long.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benhlina/Library/CloudStorage/Dropbox/GitHub/GLATAR-App/www/data-entry-template/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6106D211-E847-7B4B-A568-5680A3C3D270}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8669748B-A5F1-7A4C-937B-207F4D7E29B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3040" yWindow="600" windowWidth="35040" windowHeight="16300" xr2:uid="{DE6F8925-643B-304C-8933-23D4A9123DA3}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="16300" xr2:uid="{DE6F8925-643B-304C-8933-23D4A9123DA3}"/>
   </bookViews>
   <sheets>
     <sheet name="data_dictionary" sheetId="1" r:id="rId1"/>
@@ -475,15 +475,6 @@
     <t>sample_procedure</t>
   </si>
   <si>
-    <t>composite</t>
-  </si>
-  <si>
-    <t>composite_n</t>
-  </si>
-  <si>
-    <t>as in: composite; format: character</t>
-  </si>
-  <si>
     <t>as in: 20; format: integer</t>
   </si>
   <si>
@@ -647,9 +638,6 @@
   </si>
   <si>
     <t xml:space="preserve">Sample origins (e.g., wild or lab) </t>
-  </si>
-  <si>
-    <t>Whether the sample is composite, an individual, or mean</t>
   </si>
   <si>
     <r>
@@ -1230,6 +1218,18 @@
   <si>
     <t>as in: 0.12; format: numeric</t>
   </si>
+  <si>
+    <t>data_type</t>
+  </si>
+  <si>
+    <t>data_type_n</t>
+  </si>
+  <si>
+    <t>as in: Individual; format: character</t>
+  </si>
+  <si>
+    <t>Whether the sample is an Individual, Composite, Mean, SD, or Equation</t>
+  </si>
 </sst>
 </file>
 
@@ -1575,13 +1575,13 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1934,20 +1934,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="48" t="s">
-        <v>211</v>
-      </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
+      <c r="A1" s="50" t="s">
+        <v>207</v>
+      </c>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
     </row>
     <row r="2" spans="1:4" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="48" t="s">
-        <v>192</v>
-      </c>
-      <c r="B2" s="48"/>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
+      <c r="A2" s="50" t="s">
+        <v>188</v>
+      </c>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="21" t="s">
@@ -1965,49 +1965,49 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="22" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="22" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="56" x14ac:dyDescent="0.2">
       <c r="A7" s="22" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="D7" s="24" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="25" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B8" s="26" t="s">
         <v>4</v>
@@ -2016,214 +2016,214 @@
         <v>66</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="28" x14ac:dyDescent="0.2">
       <c r="A9" s="25" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="28" x14ac:dyDescent="0.2">
       <c r="A10" s="25" t="s">
+        <v>88</v>
+      </c>
+      <c r="B10" s="27" t="s">
+        <v>79</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="D10" s="24" t="s">
         <v>91</v>
-      </c>
-      <c r="B10" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="C10" s="19" t="s">
-        <v>156</v>
-      </c>
-      <c r="D10" s="24" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="56" x14ac:dyDescent="0.2">
       <c r="A11" s="25" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="25" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B12" s="27" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="28" x14ac:dyDescent="0.2">
       <c r="A13" s="25" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B13" s="24" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="D13" s="24" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="25" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B14" s="27" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D14" s="24" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="25" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B15" s="24" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C15" s="24" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D15" s="24" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="25" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="25" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B17" s="24" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C17" s="24" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="D17" s="24" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" s="25" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B18" s="24" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C18" s="24" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D18" s="24" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" s="25" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B19" s="24" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C19" s="24" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D19" s="24" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="28" x14ac:dyDescent="0.2">
       <c r="A20" s="25" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B20" s="24" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D20" s="24" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" s="25" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B21" s="24" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D21" s="24" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" s="25" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B22" s="24" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C22" s="24" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="D22" s="24" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" s="28" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B23" s="29" t="s">
         <v>14</v>
       </c>
       <c r="C23" s="20" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D23" s="20" t="s">
         <v>18</v>
@@ -2231,10 +2231,10 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" s="30" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B24" s="30" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C24" s="30" t="s">
         <v>40</v>
@@ -2245,69 +2245,69 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" s="30" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B25" s="31" t="s">
         <v>70</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" s="30" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B26" s="30" t="s">
         <v>5</v>
       </c>
       <c r="C26" s="30" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="D26" s="30" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" s="30" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B27" s="30" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C27" s="30" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="D27" s="30" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" s="30" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B28" s="30" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C28" s="30" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D28" s="30" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" s="30" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B29" s="32" t="s">
         <v>6</v>
       </c>
       <c r="C29" s="30" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="D29" s="30" t="s">
         <v>11</v>
@@ -2315,55 +2315,55 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" s="30" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B30" s="32" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C30" s="30" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="D30" s="30" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" s="30" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B31" s="30" t="s">
         <v>15</v>
       </c>
       <c r="C31" s="30" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="D31" s="30" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" s="30" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B32" s="30" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C32" s="30" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D32" s="30" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" s="30" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B33" s="30" t="s">
         <v>7</v>
       </c>
       <c r="C33" s="30" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="D33" s="30" t="s">
         <v>41</v>
@@ -2371,21 +2371,21 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" s="30" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B34" s="30" t="s">
         <v>8</v>
       </c>
       <c r="C34" s="30" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="D34" s="30" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" s="30" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B35" s="32" t="s">
         <v>13</v>
@@ -2394,29 +2394,29 @@
         <v>50</v>
       </c>
       <c r="D35" s="33" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="28" x14ac:dyDescent="0.2">
       <c r="A36" s="30" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B36" s="30" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="C36" s="30" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="D36" s="33" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" s="30" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B37" s="30" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C37" s="30" t="s">
         <v>49</v>
@@ -2427,83 +2427,83 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" s="30" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="B38" s="30" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C38" s="30" t="s">
         <v>51</v>
       </c>
       <c r="D38" s="30" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="28" x14ac:dyDescent="0.2">
       <c r="A39" s="30" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="B39" s="30" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C39" s="30" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="D39" s="33" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" s="30" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B40" s="30" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C40" s="30" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D40" s="30" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="28" x14ac:dyDescent="0.2">
       <c r="A41" s="30" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B41" s="30" t="s">
-        <v>72</v>
+        <v>294</v>
       </c>
       <c r="C41" s="30" t="s">
-        <v>74</v>
-      </c>
-      <c r="D41" s="30" t="s">
-        <v>130</v>
+        <v>296</v>
+      </c>
+      <c r="D41" s="33" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" s="30" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B42" s="30" t="s">
+        <v>295</v>
+      </c>
+      <c r="C42" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="D42" s="30" t="s">
         <v>73</v>
-      </c>
-      <c r="C42" s="30" t="s">
-        <v>75</v>
-      </c>
-      <c r="D42" s="30" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" s="30" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B43" s="32" t="s">
         <v>9</v>
       </c>
       <c r="C43" s="30" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D43" s="30" t="s">
         <v>12</v>
@@ -2511,16 +2511,16 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" s="30" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B44" s="32" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C44" s="30" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D44" s="30" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
@@ -2528,13 +2528,13 @@
         <v>16</v>
       </c>
       <c r="B45" s="30" t="s">
+        <v>119</v>
+      </c>
+      <c r="C45" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="D45" s="30" t="s">
         <v>122</v>
-      </c>
-      <c r="C45" s="30" t="s">
-        <v>124</v>
-      </c>
-      <c r="D45" s="30" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
@@ -2559,10 +2559,10 @@
         <v>19</v>
       </c>
       <c r="C47" s="30" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="D47" s="30" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
@@ -2576,7 +2576,7 @@
         <v>60</v>
       </c>
       <c r="D48" s="30" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
@@ -2587,7 +2587,7 @@
         <v>21</v>
       </c>
       <c r="C49" s="30" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="D49" s="30" t="s">
         <v>61</v>
@@ -2601,7 +2601,7 @@
         <v>22</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>26</v>
@@ -2615,10 +2615,10 @@
         <v>23</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.2">
@@ -2640,13 +2640,13 @@
         <v>28</v>
       </c>
       <c r="B53" s="34" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
@@ -2654,13 +2654,13 @@
         <v>28</v>
       </c>
       <c r="B54" s="30" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C54" s="30" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D54" s="30" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
@@ -2668,13 +2668,13 @@
         <v>28</v>
       </c>
       <c r="B55" s="30" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C55" s="30" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="D55" s="30" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
@@ -2682,13 +2682,13 @@
         <v>28</v>
       </c>
       <c r="B56" s="30" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C56" s="30" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D56" s="30" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
@@ -2696,13 +2696,13 @@
         <v>28</v>
       </c>
       <c r="B57" s="35" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C57" s="30" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="D57" s="30" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
@@ -2710,13 +2710,13 @@
         <v>28</v>
       </c>
       <c r="B58" s="30" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C58" s="30" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D58" s="30" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
@@ -2724,13 +2724,13 @@
         <v>28</v>
       </c>
       <c r="B59" s="30" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C59" s="30" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="D59" s="30" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
@@ -2738,13 +2738,13 @@
         <v>28</v>
       </c>
       <c r="B60" s="35" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C60" s="30" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="D60" s="30" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
@@ -2752,13 +2752,13 @@
         <v>28</v>
       </c>
       <c r="B61" s="35" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C61" s="30" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D61" s="30" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
@@ -2892,13 +2892,13 @@
         <v>39</v>
       </c>
       <c r="B71" s="30" t="s">
+        <v>218</v>
+      </c>
+      <c r="C71" s="30" t="s">
         <v>222</v>
       </c>
-      <c r="C71" s="30" t="s">
-        <v>226</v>
-      </c>
       <c r="D71" s="30" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.2">
@@ -2906,13 +2906,13 @@
         <v>39</v>
       </c>
       <c r="B72" s="30" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="C72" s="30" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="D72" s="30" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.2">
@@ -2920,279 +2920,279 @@
         <v>39</v>
       </c>
       <c r="B73" s="30" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C73" s="30" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D73" s="30" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A74" s="30" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="B74" s="30" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="C74" s="30" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="D74" s="30" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
     </row>
     <row r="75" spans="1:4" ht="28" x14ac:dyDescent="0.2">
       <c r="A75" s="33" t="s">
+        <v>224</v>
+      </c>
+      <c r="B75" s="33" t="s">
         <v>228</v>
       </c>
-      <c r="B75" s="33" t="s">
-        <v>232</v>
-      </c>
       <c r="C75" s="33" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="D75" s="33" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A76" s="33" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="B76" s="33" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="C76" s="33" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="D76" s="33" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
     </row>
     <row r="77" spans="1:4" ht="28" x14ac:dyDescent="0.2">
       <c r="A77" s="33" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="B77" s="34" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="C77" s="33" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="D77" s="33" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="42" x14ac:dyDescent="0.2">
       <c r="A78" s="33" t="s">
+        <v>234</v>
+      </c>
+      <c r="B78" s="34" t="s">
         <v>238</v>
       </c>
-      <c r="B78" s="34" t="s">
-        <v>242</v>
-      </c>
       <c r="C78" s="33" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="D78" s="33" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A79" s="30" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="B79" s="35" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C79" s="30" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="D79" s="30" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A80" s="30" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="B80" s="30" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="C80" s="30" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="D80" s="33" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
     </row>
     <row r="81" spans="1:4" ht="42" x14ac:dyDescent="0.2">
       <c r="A81" s="30" t="s">
+        <v>244</v>
+      </c>
+      <c r="B81" s="30" t="s">
+        <v>247</v>
+      </c>
+      <c r="C81" s="30" t="s">
+        <v>239</v>
+      </c>
+      <c r="D81" s="33" t="s">
         <v>248</v>
-      </c>
-      <c r="B81" s="30" t="s">
-        <v>251</v>
-      </c>
-      <c r="C81" s="30" t="s">
-        <v>243</v>
-      </c>
-      <c r="D81" s="33" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A82" s="30" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="B82" s="30" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="C82" s="30" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="D82" s="33" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A83" s="30" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="B83" s="30" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="C83" s="30" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D83" s="30" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
     </row>
     <row r="84" spans="1:4" ht="28" x14ac:dyDescent="0.2">
       <c r="A84" s="30" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="B84" s="40" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C84" s="30" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="D84" s="33" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
     </row>
     <row r="85" spans="1:4" ht="42" x14ac:dyDescent="0.2">
       <c r="A85" s="30" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="B85" s="40" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="C85" s="30" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="D85" s="33" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A86" s="30" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="B86" s="40" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="C86" s="30" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D86" s="30" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A87" s="30" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="B87" s="40" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="C87" s="30" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="D87" s="30" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A88" s="30" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="B88" s="30" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="C88" s="30" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="D88" s="30" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A89" s="30" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="B89" s="30" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="C89" s="30" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="D89" s="30" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A90" s="30" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="B90" s="30" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="C90" s="30" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="D90" s="30" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A91" s="30" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="B91" s="30" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="C91" s="30" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="D91" s="30" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A92" s="30" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="B92" s="30" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="C92" s="30" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="D92" s="30" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -3216,40 +3216,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="19" x14ac:dyDescent="0.25">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="48" t="s">
+        <v>198</v>
+      </c>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="10" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" s="48" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="49"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="11"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" s="48"/>
+      <c r="B3" s="48"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="11" t="s">
         <v>202</v>
-      </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="10" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="49" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="11"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="49"/>
-      <c r="B3" s="49"/>
-      <c r="C3" s="49"/>
-      <c r="D3" s="11" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="13" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -3282,76 +3282,76 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="19" x14ac:dyDescent="0.25">
-      <c r="A1" s="49" t="s">
-        <v>190</v>
-      </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
+      <c r="A1" s="48" t="s">
+        <v>186</v>
+      </c>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
       <c r="D1" s="10" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A2" s="49" t="s">
+      <c r="A2" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
+      <c r="B2" s="49"/>
+      <c r="C2" s="49"/>
       <c r="D2" s="11"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A3" s="49"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="50"/>
+      <c r="A3" s="48"/>
+      <c r="B3" s="49"/>
+      <c r="C3" s="49"/>
       <c r="D3" s="11" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" s="15" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="B4" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E4" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="F4" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="G4" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E4" s="16" t="s">
+      <c r="I4" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="K4" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="L4" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="G4" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="H4" s="2" t="s">
+      <c r="M4" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="I4" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="K4" s="2" t="s">
+      <c r="N4" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="O4" s="2" t="s">
         <v>87</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="O4" s="2" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.2">
@@ -44260,7 +44260,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED99CF4A-5D49-794D-A1CB-3B08F37AF445}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:BT22"/>
+  <dimension ref="A1:BT14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20.5" customWidth="1"/>
@@ -44276,6 +44276,7 @@
     <col min="15" max="15" width="12" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="8.1640625" style="8" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="9" style="8" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="11" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="15.5" style="8" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="15.5" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="15.5" customWidth="1"/>
@@ -44312,34 +44313,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:72" ht="19" x14ac:dyDescent="0.25">
-      <c r="A1" s="49" t="s">
-        <v>189</v>
-      </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
+      <c r="A1" s="48" t="s">
+        <v>185</v>
+      </c>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
       <c r="D1" s="5" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
     </row>
     <row r="2" spans="1:72" x14ac:dyDescent="0.2">
-      <c r="A2" s="49" t="s">
+      <c r="A2" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
+      <c r="B2" s="49"/>
+      <c r="C2" s="49"/>
       <c r="D2" s="6"/>
     </row>
     <row r="3" spans="1:72" x14ac:dyDescent="0.2">
-      <c r="A3" s="49"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="50"/>
+      <c r="A3" s="48"/>
+      <c r="B3" s="49"/>
+      <c r="C3" s="49"/>
       <c r="D3" s="6" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:72" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="X4" t="s">
         <v>16</v>
@@ -44354,29 +44355,29 @@
         <v>39</v>
       </c>
       <c r="BB4" s="37" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="BC4" s="37"/>
       <c r="BD4" s="37"/>
       <c r="BE4" s="37" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="BF4" s="37"/>
       <c r="BG4" s="37"/>
       <c r="BH4" s="37" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="BI4" s="38"/>
       <c r="BJ4" s="38"/>
       <c r="BK4" s="38" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="BL4" s="38"/>
       <c r="BM4" s="38"/>
       <c r="BN4" s="38"/>
       <c r="BO4" s="38"/>
       <c r="BP4" s="38" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="BQ4" s="38"/>
       <c r="BR4" s="38"/>
@@ -44388,37 +44389,37 @@
         <v>14</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C5" s="36" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D5" s="43" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E5" s="36" t="s">
         <v>65</v>
       </c>
       <c r="F5" s="36" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="G5" s="36" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="H5" s="44" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="I5" s="44" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="J5" s="36" t="s">
         <v>15</v>
       </c>
       <c r="K5" s="36" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="L5" s="36" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="M5" s="36" t="s">
         <v>8</v>
@@ -44427,25 +44428,25 @@
         <v>13</v>
       </c>
       <c r="O5" s="36" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="P5" s="36" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="Q5" s="36" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="R5" s="36" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="S5" s="36" t="s">
-        <v>201</v>
-      </c>
-      <c r="T5" s="45" t="s">
-        <v>72</v>
+        <v>197</v>
+      </c>
+      <c r="T5" s="46" t="s">
+        <v>294</v>
       </c>
       <c r="U5" s="45" t="s">
-        <v>73</v>
+        <v>295</v>
       </c>
       <c r="V5" s="44" t="s">
         <v>9</v>
@@ -44454,7 +44455,7 @@
         <v>71</v>
       </c>
       <c r="X5" s="45" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="Y5" s="44" t="s">
         <v>17</v>
@@ -44469,40 +44470,40 @@
         <v>21</v>
       </c>
       <c r="AC5" s="47" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="AD5" s="47" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="AE5" s="47" t="s">
         <v>67</v>
       </c>
       <c r="AF5" s="47" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="AG5" s="36" t="s">
+        <v>134</v>
+      </c>
+      <c r="AH5" s="36" t="s">
+        <v>112</v>
+      </c>
+      <c r="AI5" s="36" t="s">
         <v>138</v>
       </c>
-      <c r="AH5" s="36" t="s">
-        <v>115</v>
-      </c>
-      <c r="AI5" s="36" t="s">
-        <v>142</v>
-      </c>
       <c r="AJ5" s="36" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="AK5" s="45" t="s">
+        <v>135</v>
+      </c>
+      <c r="AL5" s="45" t="s">
+        <v>136</v>
+      </c>
+      <c r="AM5" s="45" t="s">
         <v>139</v>
       </c>
-      <c r="AL5" s="45" t="s">
+      <c r="AN5" s="45" t="s">
         <v>140</v>
-      </c>
-      <c r="AM5" s="45" t="s">
-        <v>143</v>
-      </c>
-      <c r="AN5" s="45" t="s">
-        <v>144</v>
       </c>
       <c r="AO5" s="36" t="s">
         <v>29</v>
@@ -44523,7 +44524,7 @@
         <v>35</v>
       </c>
       <c r="AU5" s="36" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="AV5" s="36" t="s">
         <v>36</v>
@@ -44535,83 +44536,83 @@
         <v>38</v>
       </c>
       <c r="AY5" s="36" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="AZ5" s="36" t="s">
+        <v>221</v>
+      </c>
+      <c r="BA5" s="36" t="s">
+        <v>144</v>
+      </c>
+      <c r="BB5" s="39" t="s">
         <v>225</v>
       </c>
-      <c r="BA5" s="36" t="s">
-        <v>148</v>
-      </c>
-      <c r="BB5" s="39" t="s">
-        <v>229</v>
-      </c>
       <c r="BC5" s="39" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="BD5" s="39" t="s">
+        <v>231</v>
+      </c>
+      <c r="BE5" s="39" t="s">
         <v>235</v>
       </c>
-      <c r="BE5" s="39" t="s">
-        <v>239</v>
-      </c>
       <c r="BF5" s="39" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="BG5" s="39" t="s">
+        <v>241</v>
+      </c>
+      <c r="BH5" s="39" t="s">
         <v>245</v>
       </c>
-      <c r="BH5" s="39" t="s">
+      <c r="BI5" s="39" t="s">
+        <v>247</v>
+      </c>
+      <c r="BJ5" s="39" t="s">
         <v>249</v>
       </c>
-      <c r="BI5" s="39" t="s">
+      <c r="BK5" s="39" t="s">
         <v>251</v>
       </c>
-      <c r="BJ5" s="39" t="s">
+      <c r="BL5" s="39" t="s">
+        <v>277</v>
+      </c>
+      <c r="BM5" s="39" t="s">
+        <v>276</v>
+      </c>
+      <c r="BN5" s="39" t="s">
+        <v>278</v>
+      </c>
+      <c r="BO5" s="39" t="s">
+        <v>279</v>
+      </c>
+      <c r="BP5" s="39" t="s">
         <v>253</v>
       </c>
-      <c r="BK5" s="39" t="s">
+      <c r="BQ5" s="39" t="s">
         <v>255</v>
       </c>
-      <c r="BL5" s="39" t="s">
-        <v>281</v>
-      </c>
-      <c r="BM5" s="39" t="s">
-        <v>280</v>
-      </c>
-      <c r="BN5" s="39" t="s">
-        <v>282</v>
-      </c>
-      <c r="BO5" s="39" t="s">
-        <v>283</v>
-      </c>
-      <c r="BP5" s="39" t="s">
-        <v>257</v>
-      </c>
-      <c r="BQ5" s="39" t="s">
+      <c r="BR5" s="39" t="s">
+        <v>265</v>
+      </c>
+      <c r="BS5" s="39" t="s">
         <v>259</v>
       </c>
-      <c r="BR5" s="39" t="s">
-        <v>269</v>
-      </c>
-      <c r="BS5" s="39" t="s">
-        <v>263</v>
-      </c>
       <c r="BT5" s="39" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="19" spans="63:63" x14ac:dyDescent="0.2">
-      <c r="BK19" s="41"/>
-    </row>
-    <row r="20" spans="63:63" x14ac:dyDescent="0.2">
-      <c r="BK20" s="41"/>
-    </row>
-    <row r="21" spans="63:63" x14ac:dyDescent="0.2">
-      <c r="BK21" s="41"/>
-    </row>
-    <row r="22" spans="63:63" x14ac:dyDescent="0.2">
-      <c r="BK22" s="41"/>
+        <v>261</v>
+      </c>
+    </row>
+    <row r="11" spans="1:72" x14ac:dyDescent="0.2">
+      <c r="BK11" s="41"/>
+    </row>
+    <row r="12" spans="1:72" x14ac:dyDescent="0.2">
+      <c r="BK12" s="41"/>
+    </row>
+    <row r="13" spans="1:72" x14ac:dyDescent="0.2">
+      <c r="BK13" s="41"/>
+    </row>
+    <row r="14" spans="1:72" x14ac:dyDescent="0.2">
+      <c r="BK14" s="41"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1"/>
@@ -44623,62 +44624,62 @@
   </mergeCells>
   <dataValidations count="20">
     <dataValidation showInputMessage="1" showErrorMessage="1" errorTitle="Unknown sex " error="You have entered an unknown value for sex " promptTitle="Sex" sqref="L5" xr:uid="{61B800F7-85EA-B74C-8D79-217EB2BB8728}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R6:R999" xr:uid="{C1262AB6-4400-D04A-976B-8F918C2989AD}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI993:AI9991 AJ6:AJ992" xr:uid="{E08CD4DA-AE11-DB40-922E-0C3ECAF74329}">
+      <formula1>"Joules/g"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V993:V9992" xr:uid="{E2A68CBD-EDB8-0D48-9B6E-B29E20DC1B19}">
+      <formula1>"belly flap, blood, carcass, cleithra, eye lens, fin, gonad, liver, muscle, otolith, scale, spine, stomach, viscera, whole body, whole body (gonads removed), whole body (stomach removed)"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R6:R991" xr:uid="{C1262AB6-4400-D04A-976B-8F918C2989AD}">
       <formula1>"Total, Fork, Standard, Carapace"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L6:L999" xr:uid="{8B693881-68ED-E14E-BF9E-57D22ABE1721}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L6:L991" xr:uid="{8B693881-68ED-E14E-BF9E-57D22ABE1721}">
       <formula1>"male, female, unknown, mixed"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F6:F999" xr:uid="{DF355696-A0A3-6D45-A97F-2A26E0345658}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F6:F991" xr:uid="{DF355696-A0A3-6D45-A97F-2A26E0345658}">
       <formula1>"spring, summer, fall, winter"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N6:N999" xr:uid="{D59253B5-564B-1D47-923E-DC586A575C35}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N6:N991" xr:uid="{D59253B5-564B-1D47-923E-DC586A575C35}">
       <formula1>"wild, lab"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T6:T999" xr:uid="{C755E85C-A899-4249-A46D-96F0A4790228}">
-      <formula1>"individual, composite, mean, equation"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W6:W999" xr:uid="{618BEA16-FB85-144A-9DB4-305EFF123E53}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W6:W991" xr:uid="{618BEA16-FB85-144A-9DB4-305EFF123E53}">
       <formula1>"wet, dried"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AH6:AH999" xr:uid="{66E4A2BE-9678-EC4D-BD77-D6B9C6555CFA}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AH6:AH991" xr:uid="{66E4A2BE-9678-EC4D-BD77-D6B9C6555CFA}">
       <formula1>"wet, dry"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI1001:AI9999 AJ6:AJ1000" xr:uid="{E08CD4DA-AE11-DB40-922E-0C3ECAF74329}">
-      <formula1>"Joules/g"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AE6:AE1000" xr:uid="{9917EF8E-9D15-EA4E-B86B-60B39CF888A1}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AE6:AE992" xr:uid="{9917EF8E-9D15-EA4E-B86B-60B39CF888A1}">
       <formula1>"Parr oxygen bomb, Parr semi-micro oxygen bomb, Phillipson microbomb, Gentry-Weigert bomb, Unknown bomb, Proximate composition, Organic analysis, Wet digestion, Unknown"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M6:M1000" xr:uid="{15E17D1F-987D-C745-9314-52B2C8C66A40}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M6:M992" xr:uid="{15E17D1F-987D-C745-9314-52B2C8C66A40}">
       <formula1>"fry, larva, juvenile, adult "</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V1001:V10000" xr:uid="{E2A68CBD-EDB8-0D48-9B6E-B29E20DC1B19}">
-      <formula1>"belly flap, blood, carcass, cleithra, eye lens, fin, gonad, liver, muscle, otolith, scale, spine, stomach, viscera, whole body, whole body (gonads removed), whole body (stomach removed)"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BC6:BC10000" xr:uid="{6BCDA29E-00AD-DC44-9456-909A8798CD81}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BC6:BC9992" xr:uid="{6BCDA29E-00AD-DC44-9456-909A8798CD81}">
       <formula1>"% sample weight, % total lipids"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BD6:BD10000" xr:uid="{E7DEBB61-EEAB-5E49-BAAF-DCF74DD84173}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BD6:BD9992" xr:uid="{E7DEBB61-EEAB-5E49-BAAF-DCF74DD84173}">
       <formula1>"triscylglycerides, fatty acids, sterols, phospholipids"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BF6:BF10000" xr:uid="{A2AF2A31-EEE5-FB45-8243-B4B5BFCCD547}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BF6:BF9992" xr:uid="{A2AF2A31-EEE5-FB45-8243-B4B5BFCCD547}">
       <formula1>"ug/mg sample weight,% total fatty acid"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BG6:BG10000" xr:uid="{8DA5F666-C5FB-A546-AA7B-E8D1C34FC070}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BG6:BG9992" xr:uid="{8DA5F666-C5FB-A546-AA7B-E8D1C34FC070}">
       <formula1>"∑SFA (saturated), ∑UFA (unsaturated), ∑MUFA (monounsaturated), ∑PUFA (polyunsaturated), ∑n-3, ∑n-6, 14:0, 16:0, 18:0, 16:1n-7 (POA), 18:1n-9 (OA), 18:3n-3 (ALA), 18:4n-3 (SDA), 18:2n-6 (LIN), 20:4n-6 (ARA), 20:5n-3 (EPA), 22:5n-6 (DPA),22:6n-3 (DHA)"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BI6:BI10000" xr:uid="{5482E599-9A41-4B43-8161-73CCB1E13AC9}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BI6:BI9992" xr:uid="{5482E599-9A41-4B43-8161-73CCB1E13AC9}">
       <formula1>"ug/mg sample weight, % total protein"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BJ6:BJ10000" xr:uid="{2FF93C04-BFBA-A042-839F-6119E2726FB2}">
-      <formula1>"Alanine, Argenine, Asparatic acid, Cysteine, Cytine, Glutamic acid, Glycine, Histadine, Isoleucine, Leucine, Lysine, Methionine, Phenylalinine, Proline, Serine, Threonine, Tyosine, Valine"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BJ6:BJ9992" xr:uid="{2FF93C04-BFBA-A042-839F-6119E2726FB2}">
+      <formula1>"Alanine, Arginine, Aspartic acid, Cysteine, Cystine, Glutamic acid, Glycine, Histidine, Isoleucine, Leucine, Lysine, Methionine, Phenylalanine, Proline, Serine, Threonine, Tyrosine, Valine"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BM6:BM10000" xr:uid="{73E98200-DF79-B04A-8673-08ACB9A22C3B}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BM6:BM9992" xr:uid="{73E98200-DF79-B04A-8673-08ACB9A22C3B}">
       <formula1>"Th (free thiamine), TMP (thiamine monophosphate), TPP (thiamine pyrophosphate), TTh (total thiamine)"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V6:V1000" xr:uid="{46AB659B-2A50-3441-8038-5315F30CB679}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V6:V992" xr:uid="{46AB659B-2A50-3441-8038-5315F30CB679}">
       <formula1>"belly flap, blood, carcass, cleithra, egg, eye lens, fin, gonad, heart, liver, muscle, otolith, scale, spine, stomach, viscera, whole body, whole body (gonads removed), whole body (stomach removed)"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T6:T10000" xr:uid="{51C4B292-4D0C-024D-B22F-A10ACA6AD19D}">
+      <formula1>"Individual, Composite, Mean, SD, Equation"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
